--- a/Sample_Project/設計書/A1_プロジェクト管理システム/020_方式設計/020_開発標準/020_テスト標準/単体テスト仕様書(Webサービス)_(取引ID)_(取引名).xlsx
+++ b/Sample_Project/設計書/A1_プロジェクト管理システム/020_方式設計/020_開発標準/020_テスト標準/単体テスト仕様書(Webサービス)_(取引ID)_(取引名).xlsx
@@ -10795,8 +10795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -10837,8 +10837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -10873,8 +10873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -10911,8 +10911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -10945,8 +10945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -10979,8 +10979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -11013,8 +11013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -11047,8 +11047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -11085,8 +11085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -11119,8 +11119,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -11153,8 +11153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -11189,8 +11189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -11223,8 +11223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -11257,8 +11257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -11291,8 +11291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -11329,8 +11329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -11363,8 +11363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -11401,8 +11401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -11435,8 +11435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -11471,8 +11471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -11505,8 +11505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -11539,8 +11539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -11573,8 +11573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -11609,8 +11609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -11643,8 +11643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -11679,8 +11679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -11717,8 +11717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -11749,8 +11749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -11781,8 +11781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -11813,8 +11813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -11849,8 +11849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -11881,8 +11881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -11923,8 +11923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -11957,8 +11957,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -11991,8 +11991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -12027,8 +12027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -12061,8 +12061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -12095,8 +12095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -12131,8 +12131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -12165,8 +12165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -12201,8 +12201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -12235,8 +12235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -12269,8 +12269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -12303,8 +12303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -12337,8 +12337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -12371,8 +12371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -12407,8 +12407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -12443,8 +12443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -12479,8 +12479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -12517,8 +12517,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -12551,8 +12551,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -12585,8 +12585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -12619,8 +12619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -12653,8 +12653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -12689,8 +12689,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -12723,8 +12723,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -12757,8 +12757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -12791,8 +12791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -12825,8 +12825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -12859,8 +12859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -12893,8 +12893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -12927,8 +12927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -12963,8 +12963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -12999,8 +12999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -13033,8 +13033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -13067,8 +13067,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -13101,8 +13101,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -13135,8 +13135,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -13175,8 +13175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -13209,8 +13209,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -13245,8 +13245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -13281,8 +13281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -13315,8 +13315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -13351,8 +13351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -13387,8 +13387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -13427,8 +13427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -13463,8 +13463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -13499,8 +13499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -13539,8 +13539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -13573,8 +13573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -13609,8 +13609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -13645,8 +13645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -13679,8 +13679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -13715,8 +13715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -13755,8 +13755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -13789,8 +13789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -13823,8 +13823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -13857,8 +13857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -13891,8 +13891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -13927,8 +13927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -13961,8 +13961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -13995,8 +13995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -14029,8 +14029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -14063,8 +14063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -14099,8 +14099,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -14141,8 +14141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -14181,8 +14181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -14215,8 +14215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -14255,8 +14255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -14295,8 +14295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -14329,8 +14329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -14371,8 +14371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -14407,8 +14407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -14441,8 +14441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -14475,8 +14475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -14511,8 +14511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -14545,8 +14545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -14579,8 +14579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -14613,8 +14613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -14647,8 +14647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -14683,8 +14683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -14717,8 +14717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -14751,8 +14751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -14785,8 +14785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -14819,8 +14819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -14855,8 +14855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -14893,8 +14893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -14933,8 +14933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -14969,8 +14969,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -15003,8 +15003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -15037,8 +15037,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -15079,8 +15079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -15115,8 +15115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -15149,8 +15149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -15183,8 +15183,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -15219,8 +15219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -15253,8 +15253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -15291,8 +15291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -15331,8 +15331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -15367,8 +15367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -15403,8 +15403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -15439,8 +15439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -15475,8 +15475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -15511,8 +15511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -15545,8 +15545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -15579,8 +15579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -15613,8 +15613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -15647,8 +15647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -15681,8 +15681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -15719,8 +15719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -15753,8 +15753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -15789,8 +15789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -15823,8 +15823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -15857,8 +15857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -15891,8 +15891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -15925,8 +15925,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -15959,8 +15959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -15993,8 +15993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -16027,8 +16027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -16061,8 +16061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -16095,8 +16095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -16129,8 +16129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -16165,8 +16165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -16199,8 +16199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -16233,8 +16233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -16267,8 +16267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -16301,8 +16301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -16335,8 +16335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -16369,8 +16369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -16405,8 +16405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -16439,8 +16439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -16473,8 +16473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -16507,8 +16507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -16541,8 +16541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -16575,8 +16575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -16609,8 +16609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -16643,8 +16643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -16677,8 +16677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -16713,8 +16713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -16749,8 +16749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -16791,8 +16791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -16829,8 +16829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -16867,8 +16867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -16909,8 +16909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -16945,8 +16945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -16979,8 +16979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -17015,8 +17015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -17049,8 +17049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -17087,8 +17087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -17127,8 +17127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -17161,8 +17161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -17195,8 +17195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -17229,8 +17229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -17263,8 +17263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -17297,8 +17297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -17331,8 +17331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -17367,8 +17367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -17405,8 +17405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -17439,8 +17439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -17473,8 +17473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -17507,8 +17507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -17541,8 +17541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -17575,8 +17575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -17609,8 +17609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -17643,8 +17643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -17677,8 +17677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -17711,8 +17711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -17745,8 +17745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -17779,8 +17779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -17813,8 +17813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -17851,8 +17851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -17885,8 +17885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -17919,8 +17919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -17953,8 +17953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -17987,8 +17987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -18021,8 +18021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -18055,8 +18055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -18089,8 +18089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -18123,8 +18123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -18157,8 +18157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -18191,8 +18191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -18225,8 +18225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -18259,8 +18259,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -18293,8 +18293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -18327,8 +18327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -18363,8 +18363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -18397,8 +18397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -18431,8 +18431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -18467,8 +18467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -18503,8 +18503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -18545,8 +18545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -18581,8 +18581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -18615,8 +18615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -18649,8 +18649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -18683,8 +18683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -18717,8 +18717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -18753,8 +18753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -18787,8 +18787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -18821,8 +18821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -18855,8 +18855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -18889,8 +18889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -18925,8 +18925,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -18965,8 +18965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -19007,8 +19007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -19041,8 +19041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -19079,8 +19079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -19113,8 +19113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -19153,8 +19153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -19189,8 +19189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -19225,8 +19225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -19261,8 +19261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -19299,8 +19299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -19333,8 +19333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -19369,8 +19369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -19403,8 +19403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -19437,8 +19437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -19471,8 +19471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -19505,8 +19505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -19539,8 +19539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -19573,8 +19573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -19607,8 +19607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -19641,8 +19641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -19675,8 +19675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -19709,8 +19709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -19745,8 +19745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -19779,8 +19779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -19813,8 +19813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -19847,8 +19847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -19881,8 +19881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -19915,8 +19915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -19951,8 +19951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -19985,8 +19985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -20019,8 +20019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -20053,8 +20053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -20087,8 +20087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -20121,8 +20121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -20155,8 +20155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -20189,8 +20189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -20225,8 +20225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -20265,8 +20265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -20297,8 +20297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -20329,8 +20329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -20361,8 +20361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -20399,8 +20399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -20433,8 +20433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -20467,8 +20467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -20501,8 +20501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -20537,8 +20537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -20569,8 +20569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -20601,8 +20601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -20633,8 +20633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -20665,8 +20665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -20697,8 +20697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -20729,8 +20729,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -20761,8 +20761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -20968,8 +20968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -21011,8 +21011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -21048,8 +21048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -21087,8 +21087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -21122,8 +21122,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -21157,8 +21157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -21192,8 +21192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -21227,8 +21227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -21266,8 +21266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -21301,8 +21301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -21336,8 +21336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -21373,8 +21373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -21408,8 +21408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -21443,8 +21443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -21478,8 +21478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -21517,8 +21517,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -21552,8 +21552,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -21591,8 +21591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -21626,8 +21626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -21663,8 +21663,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -21698,8 +21698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -21733,8 +21733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -21768,8 +21768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -21805,8 +21805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -21840,8 +21840,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -21877,8 +21877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -21918,8 +21918,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -21953,8 +21953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -21988,8 +21988,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -22023,8 +22023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -22062,8 +22062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -22097,8 +22097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -22136,8 +22136,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -22169,8 +22169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -22206,8 +22206,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -22239,8 +22239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -22280,8 +22280,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -22313,8 +22313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-3-1</v>
       </c>
@@ -22346,8 +22346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -22381,8 +22381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -22414,8 +22414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -22447,8 +22447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -22482,8 +22482,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-2-1</v>
       </c>
@@ -22515,8 +22515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -22550,8 +22550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-2-1</v>
       </c>
@@ -22583,8 +22583,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-3-1</v>
       </c>
@@ -22616,8 +22616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-4-1</v>
       </c>
@@ -22649,8 +22649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-5-1</v>
       </c>
@@ -22682,8 +22682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-6-1</v>
       </c>
@@ -22715,8 +22715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -22750,8 +22750,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -22785,8 +22785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -22820,8 +22820,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -22857,8 +22857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-2-1</v>
       </c>
@@ -22890,8 +22890,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-3-1</v>
       </c>
@@ -22923,8 +22923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-4-1</v>
       </c>
@@ -22956,8 +22956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-5-1</v>
       </c>
@@ -22989,8 +22989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -23024,8 +23024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -23057,8 +23057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -23090,8 +23090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -23123,8 +23123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -23156,8 +23156,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-6-1</v>
       </c>
@@ -23189,8 +23189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-7-1</v>
       </c>
@@ -23222,8 +23222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-8-1</v>
       </c>
@@ -23255,8 +23255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -23290,8 +23290,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -23325,8 +23325,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-2-1</v>
       </c>
@@ -23358,8 +23358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-3-1</v>
       </c>
@@ -23391,8 +23391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-4-1</v>
       </c>
@@ -23424,8 +23424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-5-1</v>
       </c>
@@ -23459,8 +23459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -23498,8 +23498,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -23531,8 +23531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -23566,8 +23566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -23601,8 +23601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-2-1</v>
       </c>
@@ -23634,8 +23634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -23669,8 +23669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -23704,8 +23704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -23743,8 +23743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -23778,8 +23778,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -23813,8 +23813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -23852,8 +23852,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -23885,8 +23885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -23920,8 +23920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -23955,8 +23955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -23988,8 +23988,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -24023,8 +24023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -24062,8 +24062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-2-1</v>
       </c>
@@ -24095,8 +24095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-3-1</v>
       </c>
@@ -24128,8 +24128,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-4-1</v>
       </c>
@@ -24161,8 +24161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-5-1</v>
       </c>
@@ -24194,8 +24194,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -24229,8 +24229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-2-1</v>
       </c>
@@ -24262,8 +24262,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-3-1</v>
       </c>
@@ -24295,8 +24295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-4-1</v>
       </c>
@@ -24328,8 +24328,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-5-1</v>
       </c>
@@ -24361,8 +24361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -24396,8 +24396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -24437,8 +24437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -24476,8 +24476,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -24509,8 +24509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -24548,8 +24548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -24587,8 +24587,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -24620,8 +24620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -24663,8 +24663,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -24700,8 +24700,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -24735,8 +24735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -24770,8 +24770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -24807,8 +24807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-2-1</v>
       </c>
@@ -24842,8 +24842,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-3-1</v>
       </c>
@@ -24877,8 +24877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-4-1</v>
       </c>
@@ -24912,8 +24912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-5-1</v>
       </c>
@@ -24947,8 +24947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -24984,8 +24984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-2-1</v>
       </c>
@@ -25019,8 +25019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-3-1</v>
       </c>
@@ -25054,8 +25054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-4-1</v>
       </c>
@@ -25089,8 +25089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-5-1</v>
       </c>
@@ -25124,8 +25124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -25161,8 +25161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -25200,8 +25200,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -25241,8 +25241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -25278,8 +25278,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -25313,8 +25313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-3-1</v>
       </c>
@@ -25348,8 +25348,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -25391,8 +25391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-2-1</v>
       </c>
@@ -25428,8 +25428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-3-1</v>
       </c>
@@ -25463,8 +25463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-4-1</v>
       </c>
@@ -25498,8 +25498,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -25535,8 +25535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-2-1</v>
       </c>
@@ -25570,8 +25570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -25609,8 +25609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -25650,8 +25650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -25687,8 +25687,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -25724,8 +25724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -25761,8 +25761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -25798,8 +25798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -25835,8 +25835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -25870,8 +25870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -25905,8 +25905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -25940,8 +25940,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -25975,8 +25975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -26010,8 +26010,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -26049,8 +26049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -26084,8 +26084,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -26121,8 +26121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -26156,8 +26156,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -26191,8 +26191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -26226,8 +26226,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -26261,8 +26261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -26296,8 +26296,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -26331,8 +26331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -26366,8 +26366,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -26401,8 +26401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-10-1</v>
       </c>
@@ -26436,8 +26436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-11-1</v>
       </c>
@@ -26471,8 +26471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -26508,8 +26508,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-2-1</v>
       </c>
@@ -26543,8 +26543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-3-1</v>
       </c>
@@ -26578,8 +26578,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-4-1</v>
       </c>
@@ -26613,8 +26613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-5-1</v>
       </c>
@@ -26648,8 +26648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-6-1</v>
       </c>
@@ -26683,8 +26683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-7-1</v>
       </c>
@@ -26718,8 +26718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -26755,8 +26755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-2-1</v>
       </c>
@@ -26790,8 +26790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-3-1</v>
       </c>
@@ -26825,8 +26825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-4-1</v>
       </c>
@@ -26860,8 +26860,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-5-1</v>
       </c>
@@ -26895,8 +26895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-6-1</v>
       </c>
@@ -26930,8 +26930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-7-1</v>
       </c>
@@ -26965,8 +26965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-8-1</v>
       </c>
@@ -27000,8 +27000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-9-1</v>
       </c>
@@ -27035,8 +27035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -27072,8 +27072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -27109,8 +27109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -27152,8 +27152,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -27191,8 +27191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -27230,8 +27230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -27273,8 +27273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -27310,8 +27310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-2-1</v>
       </c>
@@ -27345,8 +27345,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -27382,8 +27382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -27417,8 +27417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -27456,8 +27456,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -27497,8 +27497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -27532,8 +27532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -27567,8 +27567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -27602,8 +27602,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -27637,8 +27637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -27672,8 +27672,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -27707,8 +27707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -27744,8 +27744,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -27783,8 +27783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -27818,8 +27818,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -27853,8 +27853,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-4-1</v>
       </c>
@@ -27888,8 +27888,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-5-1</v>
       </c>
@@ -27923,8 +27923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-6-1</v>
       </c>
@@ -27958,8 +27958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-7-1</v>
       </c>
@@ -27993,8 +27993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-8-1</v>
       </c>
@@ -28028,8 +28028,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-9-1</v>
       </c>
@@ -28063,8 +28063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-10-1</v>
       </c>
@@ -28098,8 +28098,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-11-1</v>
       </c>
@@ -28133,8 +28133,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-12-1</v>
       </c>
@@ -28168,8 +28168,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-13-1</v>
       </c>
@@ -28203,8 +28203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -28242,8 +28242,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-2-1</v>
       </c>
@@ -28277,8 +28277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-3-1</v>
       </c>
@@ -28312,8 +28312,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-4-1</v>
       </c>
@@ -28347,8 +28347,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-5-1</v>
       </c>
@@ -28382,8 +28382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-6-1</v>
       </c>
@@ -28417,8 +28417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-7-1</v>
       </c>
@@ -28452,8 +28452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-8-1</v>
       </c>
@@ -28487,8 +28487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-9-1</v>
       </c>
@@ -28522,8 +28522,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-10-1</v>
       </c>
@@ -28557,8 +28557,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-11-1</v>
       </c>
@@ -28592,8 +28592,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-12-1</v>
       </c>
@@ -28627,8 +28627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-13-1</v>
       </c>
@@ -28662,8 +28662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-14-1</v>
       </c>
@@ -28697,8 +28697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-15-1</v>
       </c>
@@ -28732,8 +28732,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -28769,8 +28769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-2-1</v>
       </c>
@@ -28804,8 +28804,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-3-1</v>
       </c>
@@ -28839,8 +28839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -28876,8 +28876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -28913,8 +28913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -28956,8 +28956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -28993,8 +28993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-2-1</v>
       </c>
@@ -29028,8 +29028,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-3-1</v>
       </c>
@@ -29063,8 +29063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-4-1</v>
       </c>
@@ -29098,8 +29098,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-5-1</v>
       </c>
@@ -29133,8 +29133,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -29170,8 +29170,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-2-1</v>
       </c>
@@ -29205,8 +29205,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-3-1</v>
       </c>
@@ -29240,8 +29240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-4-1</v>
       </c>
@@ -29275,8 +29275,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-5-1</v>
       </c>
@@ -29310,8 +29310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -29347,8 +29347,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -29388,8 +29388,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -29431,8 +29431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-2-1</v>
       </c>
@@ -29466,8 +29466,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -29505,8 +29505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-2-1</v>
       </c>
@@ -29540,8 +29540,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -29581,8 +29581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -29618,8 +29618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -29655,8 +29655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -29692,8 +29692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -29731,8 +29731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -29766,8 +29766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -29803,8 +29803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -29838,8 +29838,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -29873,8 +29873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -29908,8 +29908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -29943,8 +29943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -29978,8 +29978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -30013,8 +30013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -30048,8 +30048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-9-1</v>
       </c>
@@ -30083,8 +30083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-10-1</v>
       </c>
@@ -30118,8 +30118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-11-1</v>
       </c>
@@ -30153,8 +30153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -30190,8 +30190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-2-1</v>
       </c>
@@ -30225,8 +30225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-3-1</v>
       </c>
@@ -30260,8 +30260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-4-1</v>
       </c>
@@ -30295,8 +30295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-5-1</v>
       </c>
@@ -30330,8 +30330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-6-1</v>
       </c>
@@ -30365,8 +30365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -30402,8 +30402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -30437,8 +30437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -30472,8 +30472,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -30507,8 +30507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-5-1</v>
       </c>
@@ -30542,8 +30542,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-6-1</v>
       </c>
@@ -30577,8 +30577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-7-1</v>
       </c>
@@ -30612,8 +30612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-8-1</v>
       </c>
@@ -30647,8 +30647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -30684,8 +30684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -30725,8 +30725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-2-1</v>
       </c>
@@ -30758,8 +30758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-3-1</v>
       </c>
@@ -30791,8 +30791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-4-1</v>
       </c>
@@ -30824,8 +30824,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -30863,8 +30863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -30898,8 +30898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -30933,8 +30933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -30968,8 +30968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -31005,8 +31005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -31038,8 +31038,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-3-1</v>
       </c>
@@ -31071,8 +31071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-4-1</v>
       </c>
@@ -31104,8 +31104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-5-1</v>
       </c>
@@ -31137,8 +31137,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-6-1</v>
       </c>
@@ -31170,8 +31170,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-7-1</v>
       </c>
@@ -31203,8 +31203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-8-1</v>
       </c>
@@ -31236,8 +31236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-9-1</v>
       </c>
@@ -31269,8 +31269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -31312,8 +31312,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -31351,8 +31351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -31390,8 +31390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -31425,8 +31425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -31460,8 +31460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -31499,8 +31499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -31536,8 +31536,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -31575,8 +31575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-2-1</v>
       </c>
@@ -31610,8 +31610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-3-1</v>
       </c>
@@ -31645,8 +31645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-4-1</v>
       </c>
@@ -31680,8 +31680,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-5-1</v>
       </c>
@@ -31715,8 +31715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-6-1</v>
       </c>
@@ -31750,8 +31750,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-7-1</v>
       </c>
@@ -31785,8 +31785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-8-1</v>
       </c>
